--- a/Spin_Coater_Circuit/Output/BOM/Spct_v2_0_BOM.xlsx
+++ b/Spin_Coater_Circuit/Output/BOM/Spct_v2_0_BOM.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\ws\Spin_Coater_HW\Spin_Coater_Circuit\Design_File\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\ws\Spin_Coater_HW\Spin_Coater_Circuit\Output\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4905BF3-D0F0-4164-9FE2-0AF9AD055032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAA708C7-1DD1-4255-8A3E-B2E67BF664B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{13CB0453-0464-46C0-8B32-89882AD6531B}"/>
   </bookViews>
@@ -35,6 +35,9 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -48,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="222">
   <si>
     <t>Id</t>
   </si>
@@ -60,9 +63,6 @@
   </si>
   <si>
     <t>수량</t>
-  </si>
-  <si>
-    <t>지정</t>
   </si>
   <si>
     <t>J15,J16,J10</t>
@@ -1126,6 +1126,10 @@
   </si>
   <si>
     <t>https://www.eleparts.co.kr/goods/view?no=11427952</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>값</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1224,7 +1228,7 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -1233,7 +1237,7 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -1284,13 +1288,13 @@
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{7479360D-0CAD-4297-B748-9FC891AEEF40}" uniqueName="1" name="Id" queryTableFieldId="1"/>
     <tableColumn id="2" xr3:uid="{7E73CBEC-3281-4C2F-98CE-8E616FB04CA2}" uniqueName="2" name="지정자" queryTableFieldId="2" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{693D2F95-2F41-4A5D-BEAE-B6E36D71DBCF}" uniqueName="9" name="제조사" queryTableFieldId="10" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{936C30DA-4407-4B38-8143-FC2F7A59107E}" uniqueName="8" name="파트넘버" queryTableFieldId="9" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{3DB5BBF1-DB0D-4D98-8DD5-C6DCC60764EF}" uniqueName="4" name="수량" queryTableFieldId="4" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{0491741F-7C1A-4C65-A5CC-19510961096A}" uniqueName="5" name="지정" queryTableFieldId="5" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{D0217364-8E7B-450E-86E1-4EDFF96B02EC}" uniqueName="3" name="풋프린트" queryTableFieldId="3" dataDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{69893B40-5CB3-42CA-87C1-E405BE2016C5}" uniqueName="10" name="비고" queryTableFieldId="11" dataDxfId="0"/>
-    <tableColumn id="6" xr3:uid="{88BBC422-B1AC-4D78-A38A-A0590035A7D4}" uniqueName="6" name="참조 링크" queryTableFieldId="6" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{693D2F95-2F41-4A5D-BEAE-B6E36D71DBCF}" uniqueName="9" name="제조사" queryTableFieldId="10" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{936C30DA-4407-4B38-8143-FC2F7A59107E}" uniqueName="8" name="파트넘버" queryTableFieldId="9" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{3DB5BBF1-DB0D-4D98-8DD5-C6DCC60764EF}" uniqueName="4" name="수량" queryTableFieldId="4" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{0491741F-7C1A-4C65-A5CC-19510961096A}" uniqueName="5" name="값" queryTableFieldId="5" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{D0217364-8E7B-450E-86E1-4EDFF96B02EC}" uniqueName="3" name="풋프린트" queryTableFieldId="3" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{69893B40-5CB3-42CA-87C1-E405BE2016C5}" uniqueName="10" name="비고" queryTableFieldId="11" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{88BBC422-B1AC-4D78-A38A-A0590035A7D4}" uniqueName="6" name="참조 링크" queryTableFieldId="6" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1636,25 +1640,25 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>221</v>
       </c>
       <c r="G1" t="s">
         <v>2</v>
       </c>
       <c r="H1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.6">
@@ -1662,28 +1666,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="E2" s="2">
         <v>3</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.6">
@@ -1691,28 +1695,28 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="H3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="E3" s="2">
-        <v>1</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.6">
@@ -1720,26 +1724,26 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E4" s="2">
         <v>4</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.6">
@@ -1747,28 +1751,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="H5" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="E5" s="2">
-        <v>1</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.6">
@@ -1776,26 +1780,26 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E6" s="2">
-        <v>1</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.6">
@@ -1803,26 +1807,26 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E7" s="2">
         <v>3</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.6">
@@ -1830,26 +1834,26 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E8" s="2">
-        <v>1</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="G8" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.6">
@@ -1857,26 +1861,26 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="E9" s="2">
-        <v>1</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.6">
@@ -1884,26 +1888,26 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E10" s="2">
         <v>4</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.6">
@@ -1911,26 +1915,26 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E11" s="2">
         <v>2</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.6">
@@ -1938,26 +1942,26 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E12" s="2">
-        <v>1</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.6">
@@ -1965,26 +1969,26 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E13" s="2">
         <v>9</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.6">
@@ -1992,26 +1996,26 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E14" s="2">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="E14" s="2">
-        <v>1</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.6">
@@ -2019,26 +2023,26 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E15" s="2">
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.6">
@@ -2046,26 +2050,26 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E16" s="2">
         <v>3</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.6">
@@ -2073,26 +2077,26 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="E17" s="2">
-        <v>1</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.6">
@@ -2100,26 +2104,26 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E18" s="2">
         <v>2</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.6">
@@ -2127,26 +2131,26 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E19" s="2">
         <v>2</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.6">
@@ -2154,26 +2158,26 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E20" s="2">
+        <v>1</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="E20" s="2">
-        <v>1</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="G20" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.6">
@@ -2181,26 +2185,26 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E21" s="2">
         <v>4</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.6">
@@ -2208,26 +2212,26 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="E22" s="2">
+        <v>1</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="E22" s="2">
-        <v>1</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="G22" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.6">
@@ -2235,26 +2239,26 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E23" s="2">
+        <v>1</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="E23" s="2">
-        <v>1</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="G23" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.6">
@@ -2262,26 +2266,26 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E24" s="2">
         <v>3</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.6">
@@ -2289,26 +2293,26 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E25" s="2">
+        <v>1</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G25" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="E25" s="2">
-        <v>1</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.6">
@@ -2316,26 +2320,26 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E26" s="2">
+        <v>1</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="E26" s="2">
-        <v>1</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="G26" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.6">
@@ -2343,28 +2347,28 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E27" s="2">
+        <v>1</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G27" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="D27" s="1" t="s">
+      <c r="H27" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>175</v>
-      </c>
-      <c r="E27" s="2">
-        <v>1</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.6">
@@ -2372,26 +2376,26 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E28" s="2">
+        <v>1</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G28" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="E28" s="2">
-        <v>1</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.6">
@@ -2399,28 +2403,28 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E29" s="2">
+        <v>1</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="D29" s="1" t="s">
+      <c r="H29" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E29" s="2">
-        <v>1</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="I29" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.6">
@@ -2428,26 +2432,26 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E30" s="2">
         <v>2</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.6">
@@ -2455,26 +2459,26 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E31" s="2">
+        <v>1</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="E31" s="2">
-        <v>1</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="G31" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.6">
@@ -2482,26 +2486,26 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E32" s="2">
+        <v>1</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G32" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="E32" s="2">
-        <v>1</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>77</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.6">
@@ -2509,26 +2513,26 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E33" s="2">
         <v>2</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.6">
@@ -2536,26 +2540,26 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E34" s="2">
+        <v>1</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="E34" s="2">
-        <v>1</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="G34" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.6">
@@ -2563,26 +2567,26 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E35" s="2">
         <v>2</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.6">
@@ -2590,26 +2594,26 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E36" s="2">
+        <v>1</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G36" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E36" s="2">
-        <v>1</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.6">
@@ -2617,26 +2621,26 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E37" s="2">
+        <v>1</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G37" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="E37" s="2">
-        <v>1</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>88</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.6">
@@ -2644,26 +2648,26 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E38" s="2">
         <v>2</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.6">
@@ -2671,26 +2675,26 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="E39" s="2">
+        <v>1</v>
+      </c>
+      <c r="F39" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="E39" s="2">
-        <v>1</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>93</v>
-      </c>
       <c r="G39" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.6">
@@ -2698,26 +2702,26 @@
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E40" s="2">
+        <v>1</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="G40" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="E40" s="2">
-        <v>1</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>95</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.6">
@@ -2725,26 +2729,26 @@
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E41" s="2">
+        <v>1</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G41" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="E41" s="2">
-        <v>1</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.6">
@@ -2752,26 +2756,26 @@
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E42" s="2">
+        <v>1</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G42" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="E42" s="2">
-        <v>1</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>100</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.6">
@@ -2779,26 +2783,26 @@
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E43" s="2">
+        <v>1</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C43" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="E43" s="2">
-        <v>1</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>103</v>
-      </c>
       <c r="G43" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.6">
@@ -2806,26 +2810,26 @@
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E44" s="2">
+        <v>1</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G44" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="E44" s="2">
-        <v>1</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>105</v>
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.6">
@@ -2833,26 +2837,26 @@
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E45" s="2">
+        <v>1</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G45" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="E45" s="2">
-        <v>1</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>108</v>
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.6">
@@ -2860,26 +2864,26 @@
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E46" s="2">
         <v>1</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.6">
@@ -2887,26 +2891,26 @@
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E47" s="2">
+        <v>1</v>
+      </c>
+      <c r="F47" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C47" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="E47" s="2">
-        <v>1</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>111</v>
-      </c>
       <c r="G47" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.6">
@@ -2914,22 +2918,22 @@
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="D48" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E48" s="2">
+        <v>1</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="G48" s="1" t="s">
         <v>207</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="E48" s="2">
-        <v>1</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>208</v>
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
